--- a/amostras/amostras_xlsx/Pesquisa_Eleitoral_Amostra_3.xlsx
+++ b/amostras/amostras_xlsx/Pesquisa_Eleitoral_Amostra_3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F32970B5-1CD2-DA4E-94CF-9D56AAFCA61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{062CBB9F-45D0-FD4B-9D2C-32C480397E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="42">
   <si>
     <t>Faixa de renda familiar</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>40 a 44 anos</t>
-  </si>
-  <si>
-    <t>Outro</t>
   </si>
   <si>
     <t>35 a 39 anos</t>
@@ -190,8 +187,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -332,7 +330,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -347,10 +345,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
@@ -370,7 +368,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
         <v>4</v>
@@ -393,7 +391,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
         <v>4</v>
@@ -416,7 +414,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
         <v>4</v>
@@ -439,7 +437,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
         <v>4</v>
@@ -462,7 +460,7 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
         <v>4</v>
@@ -485,7 +483,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
         <v>4</v>
@@ -508,7 +506,7 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
         <v>4</v>
@@ -531,7 +529,7 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
         <v>4</v>
@@ -554,7 +552,7 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
         <v>4</v>
@@ -577,7 +575,7 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>4</v>
@@ -600,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
         <v>4</v>
@@ -623,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
         <v>4</v>
@@ -646,7 +644,7 @@
         <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
         <v>4</v>
@@ -669,7 +667,7 @@
         <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s">
         <v>4</v>
@@ -692,7 +690,7 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
         <v>4</v>
@@ -715,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" t="s">
         <v>4</v>
@@ -738,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
         <v>4</v>
@@ -761,7 +759,7 @@
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
         <v>4</v>
@@ -784,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
         <v>4</v>
@@ -807,7 +805,7 @@
         <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" t="s">
         <v>4</v>
@@ -830,7 +828,7 @@
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s">
         <v>4</v>
@@ -853,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s">
         <v>4</v>
@@ -876,7 +874,7 @@
         <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s">
         <v>4</v>
@@ -899,7 +897,7 @@
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G26" t="s">
         <v>4</v>
@@ -922,7 +920,7 @@
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
         <v>4</v>
@@ -945,7 +943,7 @@
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G28" t="s">
         <v>4</v>
@@ -968,7 +966,7 @@
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
         <v>4</v>
@@ -991,7 +989,7 @@
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G30" t="s">
         <v>4</v>
@@ -1014,7 +1012,7 @@
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
         <v>4</v>
@@ -1037,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
         <v>4</v>
@@ -1060,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G36" t="s">
         <v>4</v>
@@ -1083,7 +1081,7 @@
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s">
         <v>4</v>
@@ -1106,7 +1104,7 @@
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G41" t="s">
         <v>4</v>
@@ -1129,7 +1127,7 @@
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G42" t="s">
         <v>4</v>
@@ -1152,7 +1150,7 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G43" t="s">
         <v>4</v>
@@ -1175,7 +1173,7 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G44" t="s">
         <v>4</v>
@@ -1198,7 +1196,7 @@
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G45" t="s">
         <v>4</v>
@@ -1221,7 +1219,7 @@
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G46" t="s">
         <v>4</v>
@@ -1244,7 +1242,7 @@
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G47" t="s">
         <v>4</v>
@@ -1267,7 +1265,7 @@
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G48" t="s">
         <v>4</v>
@@ -1290,7 +1288,7 @@
         <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G49" t="s">
         <v>4</v>
@@ -1313,7 +1311,7 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G50" t="s">
         <v>4</v>
@@ -1336,7 +1334,7 @@
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G51" t="s">
         <v>4</v>
@@ -1359,7 +1357,7 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G52" t="s">
         <v>4</v>
@@ -1382,7 +1380,7 @@
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G53" t="s">
         <v>4</v>
@@ -1405,7 +1403,7 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s">
         <v>4</v>
@@ -1428,7 +1426,7 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s">
         <v>4</v>
@@ -1451,7 +1449,7 @@
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G58" t="s">
         <v>4</v>
@@ -1474,7 +1472,7 @@
         <v>18</v>
       </c>
       <c r="F59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G59" t="s">
         <v>4</v>
@@ -1497,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G60" t="s">
         <v>4</v>
@@ -1520,7 +1518,7 @@
         <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G61" t="s">
         <v>4</v>
@@ -1543,7 +1541,7 @@
         <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G62" t="s">
         <v>4</v>
@@ -1566,7 +1564,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G63" t="s">
         <v>4</v>
@@ -1589,7 +1587,7 @@
         <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G64" t="s">
         <v>27</v>
@@ -1612,7 +1610,7 @@
         <v>20</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -1635,7 +1633,7 @@
         <v>29</v>
       </c>
       <c r="F67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G67" t="s">
         <v>27</v>
@@ -1658,7 +1656,7 @@
         <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G68" t="s">
         <v>4</v>
@@ -1681,7 +1679,7 @@
         <v>21</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G69" t="s">
         <v>4</v>
@@ -1704,7 +1702,7 @@
         <v>20</v>
       </c>
       <c r="F70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G70" t="s">
         <v>4</v>
@@ -1727,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G71" t="s">
         <v>4</v>
@@ -1750,7 +1748,7 @@
         <v>29</v>
       </c>
       <c r="F72" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G72" t="s">
         <v>4</v>
@@ -1773,7 +1771,7 @@
         <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G75" t="s">
         <v>4</v>
@@ -1796,7 +1794,7 @@
         <v>31</v>
       </c>
       <c r="F76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G76" t="s">
         <v>4</v>
@@ -1819,7 +1817,7 @@
         <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G77" t="s">
         <v>4</v>
@@ -1842,7 +1840,7 @@
         <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G78" t="s">
         <v>4</v>
@@ -1865,7 +1863,7 @@
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G80" t="s">
         <v>4</v>
@@ -1888,7 +1886,7 @@
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G81" t="s">
         <v>27</v>
@@ -1911,7 +1909,7 @@
         <v>26</v>
       </c>
       <c r="F82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G82" t="s">
         <v>27</v>
@@ -1934,7 +1932,7 @@
         <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G83" t="s">
         <v>27</v>
@@ -1957,7 +1955,7 @@
         <v>9</v>
       </c>
       <c r="F86" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G86" t="s">
         <v>27</v>
@@ -1980,7 +1978,7 @@
         <v>31</v>
       </c>
       <c r="F87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G87" t="s">
         <v>27</v>
@@ -2003,7 +2001,7 @@
         <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G88" t="s">
         <v>27</v>
@@ -2026,7 +2024,7 @@
         <v>34</v>
       </c>
       <c r="F89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G89" t="s">
         <v>27</v>
@@ -2049,7 +2047,7 @@
         <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G90" t="s">
         <v>27</v>
@@ -2072,7 +2070,7 @@
         <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G91" t="s">
         <v>27</v>
@@ -2095,7 +2093,7 @@
         <v>9</v>
       </c>
       <c r="F93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G93" t="s">
         <v>27</v>
@@ -2118,7 +2116,7 @@
         <v>18</v>
       </c>
       <c r="F94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G94" t="s">
         <v>27</v>
@@ -2141,7 +2139,7 @@
         <v>29</v>
       </c>
       <c r="F95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G95" t="s">
         <v>27</v>
@@ -2164,15 +2162,15 @@
         <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G96" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A99" t="s">
-        <v>36</v>
+      <c r="A99" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B99" t="s">
         <v>11</v>
@@ -2187,7 +2185,7 @@
         <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G99" t="s">
         <v>27</v>
@@ -2198,7 +2196,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2210,7 +2208,7 @@
         <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G100" t="s">
         <v>27</v>
@@ -2233,7 +2231,7 @@
         <v>12</v>
       </c>
       <c r="F101" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G101" t="s">
         <v>27</v>
